--- a/projetos/general-carneiro/saida/Matriz_Anexo_VI_general_carneiro.xlsx
+++ b/projetos/general-carneiro/saida/Matriz_Anexo_VI_general_carneiro.xlsx
@@ -739,16 +739,12 @@
           <t>2 Identificação do Empreendimento</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>PARCIALMENTE ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>A VERIFICAR: empreendedor.responsavel; A VERIFICAR: função; A VERIFICAR: registro; A VERIFICAR: empreendedor.telefone</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -766,14 +762,14 @@
           <t>2 Identificação do Empreendimento</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>PARCIALMENTE ATENDIDO</t>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>NÃO ATENDIDO</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: empreendedor.email</t>
+          <t>Informação não localizada na seção.</t>
         </is>
       </c>
     </row>
@@ -807,7 +803,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: area.total_m2; A VERIFICAR: area.construida_m2; A VERIFICAR: area.livre_m2</t>
+          <t>A VERIFICAR: area.construida_m2; A VERIFICAR: area.livre_m2</t>
         </is>
       </c>
     </row>
@@ -827,12 +823,16 @@
           <t>3.3 Coordenadas Geográficas e UTM</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/localizacao_unidades.png; arquivo ausente: mapas/localizacao_regional.png</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -850,12 +850,16 @@
           <t>3.5.1 Pedologia</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/solos.png; arquivo ausente: mapas/uso_solo.png</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -873,12 +877,16 @@
           <t>3.5.2 Geomorfologia</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/geomorfologia.png; arquivo ausente: mapas/altimetria.png; arquivo ausente: mapas/declividade.png</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -903,7 +911,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: área de drenagem e uso do solo da bacia.; A VERIFICAR: manancial.classe; A VERIFICAR: área da bacia de contribuição no ponto de captação e cursos d'água interceptados pelas adutoras.</t>
+          <t>A VERIFICAR: manancial.classe; A VERIFICAR: área da bacia de contribuição no ponto de captação e cursos d'água interceptados pelas adutoras.; arquivo ausente: mapas/bacia.png</t>
         </is>
       </c>
     </row>
@@ -923,12 +931,16 @@
           <t>3.5.4 Geologia; 3.5.5 Hidrogeologia</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/geologia.png; arquivo ausente: mapas/hidrogeologia.png</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -953,7 +965,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: ocorrência de Reserva Legal nos imóveis afetados, conforme CAR/SICAR – colocar os arquivos do CAR em dados/car/ e regenerar o mapa.</t>
+          <t>arquivo ausente: mapas/fitogeografia.png; A VERIFICAR: Reserva Legal – baixar no SICAR os shapes do CAR dos imóveis atravessados para dados/car/ e regenerar o mapa e o texto.; arquivo ausente: mapas/app_rl.png</t>
         </is>
       </c>
     </row>
@@ -980,7 +992,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: rodovia de acesso principal e condições de tráfego/pavimentação até as unidades.; A VERIFICAR: alternativas de acesso a cada unidade (urbana e rural), com figuras.</t>
+          <t>arquivo ausente: mapas/acesso_1.png</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1012,16 @@
           <t>3.5.1.1 Uso do Solo; 3.7.1 Residências, condições do entorno</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/uso_solo.png; A VERIFICAR: fotos de campo das vias de acesso e do entorno (pavimentação, residências, igrejas) – colocar em fotos/brutas/, rodar python -m ferramentas.imagens.fotos e o redator.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1030,12 +1046,16 @@
           <t>3.3 Coordenadas Geográficas e UTM</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/localizacao_unidades.png</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1161,12 +1181,16 @@
           <t>3.5.3 Hidrologia</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>ATENDIDO</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE ATENDIDO</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>arquivo ausente: mapas/bacia.png</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1191,7 +1215,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: ocorrência de Reserva Legal nos imóveis afetados, conforme CAR/SICAR – colocar os arquivos do CAR em dados/car/ e regenerar o mapa.</t>
+          <t>arquivo ausente: mapas/fitogeografia.png; A VERIFICAR: Reserva Legal – baixar no SICAR os shapes do CAR dos imóveis atravessados para dados/car/ e regenerar o mapa e o texto.; arquivo ausente: mapas/app_rl.png</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1242,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: ocorrência de Reserva Legal nos imóveis afetados, conforme CAR/SICAR – colocar os arquivos do CAR em dados/car/ e regenerar o mapa.</t>
+          <t>A VERIFICAR: Reserva Legal – baixar no SICAR os shapes do CAR dos imóveis atravessados para dados/car/ e regenerar o mapa e o texto.; arquivo ausente: mapas/app_rl.png</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1269,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>A VERIFICAR: ocorrência de Reserva Legal nos imóveis afetados, conforme CAR/SICAR – colocar os arquivos do CAR em dados/car/ e regenerar o mapa.</t>
+          <t>A VERIFICAR: Reserva Legal – baixar no SICAR os shapes do CAR dos imóveis atravessados para dados/car/ e regenerar o mapa e o texto.; arquivo ausente: mapas/app_rl.png</t>
         </is>
       </c>
     </row>
@@ -1567,13 +1591,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1586,10 +1610,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1605,10 +1629,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1643,13 +1667,13 @@
         <v>36</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
